--- a/profiles/ro-crate-masp/profile-crate/ro-crate-metadata.xlsx
+++ b/profiles/ro-crate-masp/profile-crate/ro-crate-metadata.xlsx
@@ -779,12 +779,18 @@
     <t>Canonical identifiers that indicate conformance to this profile.</t>
   </si>
   <si>
+    <t>https://www.nationalarchives.gov.uk/PRONOM/fmt/471</t>
+  </si>
+  <si>
+    <t>DigitalFormat</t>
+  </si>
+  <si>
+    <t>Hypertext Markup Language</t>
+  </si>
+  <si>
     <t>https://www.nationalarchives.gov.uk/PRONOM/fmt/1149</t>
   </si>
   <si>
-    <t>DigitalFormat</t>
-  </si>
-  <si>
     <t>Markdown</t>
   </si>
   <si>
@@ -792,12 +798,6 @@
   </si>
   <si>
     <t>JSON Data Interchange Format</t>
-  </si>
-  <si>
-    <t>https://www.nationalarchives.gov.uk/PRONOM/fmt/471</t>
-  </si>
-  <si>
-    <t>Hypertext Markup Language</t>
   </si>
 </sst>
 </file>

--- a/profiles/ro-crate-masp/profile-crate/ro-crate-metadata.xlsx
+++ b/profiles/ro-crate-masp/profile-crate/ro-crate-metadata.xlsx
@@ -443,7 +443,7 @@
     <t>"#class_MetadataDescriptor"</t>
   </si>
   <si>
-    <t>["Text", "#propertyValue_prop_id_MetadataDescriptor"]</t>
+    <t>"#propertyValue_prop_id_MetadataDescriptor"</t>
   </si>
   <si>
     <t>#prop_conformsTo_MetadataDescriptor</t>
